--- a/output/2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -498,7 +498,6 @@
           <t>04-772 6988</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Confermato da directory (D&amp;B, CTOS, EMIS) e sito ufficiale. Nota: fonte originale riporta 04-772 6988, verifica indipendente ha trovato anche 04-772 1988 - confermare numero aggiornato prima di contattare.</t>
@@ -585,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Confermata da EMIS, NEWPAGES e sito ufficiale; azienda attiva dal 1983.</t>
+          <t>Confermata da EMIS, NEWPAGES e sito ufficiale; azienda attiva dal 1983. [DUPLICATO — vedi anche: 2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -600,7 +599,6 @@
           <t>HE Machinery And Tools Trading (Alor Setar) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Kedah (Alor Setar)</t>
@@ -623,7 +621,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confermata come dealer ufficiale su 4 pagine brand distinte (Husqvarna, GL Bosun, DongCheng, Makita) - alta affidabilita. Nessun sito proprio trovato.</t>
+          <t>Confermata come dealer ufficiale su 4 pagine brand distinte (Husqvarna, GL Bosun, DongCheng, Makita) - alta affidabilita. Nessun sito proprio trovato. [DUPLICATO — vedi anche: 2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -638,7 +636,6 @@
           <t>CR Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kedah (Kulim)</t>
@@ -654,7 +651,6 @@
           <t>013-532 4038</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermata come authorized dealer su pagine ufficiali GL Bosun e DongCheng. Numero secondario 017-4156860 da fonte originale non riconfermato separatamente.</t>
@@ -672,7 +668,6 @@
           <t>Kian Hock Power Tools Service</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Kedah (Sungai Petani)</t>
@@ -695,7 +690,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confermata come dealer ufficiale su pagine Makita.my e Akaido.com.my. Email da fonte originale, non riscontrata autonomamente in verifica.</t>
+          <t>Confermata come dealer ufficiale su pagine Makita.my e Akaido.com.my. Email da fonte originale, non riscontrata autonomamente in verifica. [DUPLICATO — vedi anche: 2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,7 +705,6 @@
           <t>Yeo Cheng Choon Hardware &amp; Machinery Sdn Bhd (filiale Kulim)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Kedah (Kulim)</t>
@@ -726,7 +720,6 @@
           <t>+60 12-423 8507</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Esistenza confermata (CTOS, companieshouse.my, MDEX, SSM reg. 62752-V dal 1980); sede principale a Segamat (Johor), filiale Kulim confermata in directory. Affidabilita media, categoria prodotto non dettagliata.</t>
@@ -744,7 +737,6 @@
           <t>Zicsano Machinery Electric</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Kedah (Alor Setar)</t>
@@ -809,7 +801,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATTENZIONE AREA: sede legale/operativa principale in Penang (Butterworth), non in Kedah. Il sito ufficiale dichiara esplicitamente copertura su Alor Setar/Jitra, Kedah. Valutare se il criterio e sede legale o area di copertura commerciale prima dell'outreach.</t>
+          <t>ATTENZIONE AREA: sede legale/operativa principale in Penang (Butterworth), non in Kedah. Il sito ufficiale dichiara esplicitamente copertura su Alor Setar/Jitra, Kedah. Valutare se il criterio e sede legale o area di copertura commerciale prima dell'outreach. [DUPLICATO — vedi anche: 2026-10-01_04_Malesia_Kedah_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/output/2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
